--- a/data/trans_dic/P55$familiar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,14</t>
+          <t>0,0; 62,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,6</t>
+          <t>0,0; 42,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,5</t>
+          <t>0,0; 60,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 64,49</t>
+          <t>21,55; 65,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,57</t>
+          <t>0,0; 68,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,6; 72,71</t>
+          <t>31,8; 71,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,5</t>
+          <t>0,0; 32,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,62</t>
+          <t>0,0; 38,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,12</t>
+          <t>0,0; 45,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,36; 61,5</t>
+          <t>32,17; 62,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,53</t>
+          <t>0,0; 48,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 57,12</t>
+          <t>7,55; 58,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,77; 68,31</t>
+          <t>29,27; 67,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,13</t>
+          <t>0,0; 60,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,53; 65,5</t>
+          <t>27,79; 65,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 39,12</t>
+          <t>4,49; 38,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 38,23</t>
+          <t>4,7; 43,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,98; 60,91</t>
+          <t>33,73; 61,45</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 55,18</t>
+          <t>10,29; 51,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,98; 43,55</t>
+          <t>7,23; 42,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 34,81</t>
+          <t>4,39; 35,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,97; 66,65</t>
+          <t>33,51; 67,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,68</t>
+          <t>0,0; 66,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,7; 65,25</t>
+          <t>16,97; 65,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 50,53</t>
+          <t>7,22; 52,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,64; 72,16</t>
+          <t>38,91; 71,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,8; 48,63</t>
+          <t>11,39; 46,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17,37; 46,85</t>
+          <t>16,39; 45,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 37,0</t>
+          <t>7,74; 36,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,49; 64,48</t>
+          <t>41,66; 64,85</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,37; 23,66</t>
+          <t>8,99; 24,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,69; 34,95</t>
+          <t>13,41; 33,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,78; 42,63</t>
+          <t>18,27; 42,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,04; 68,33</t>
+          <t>49,63; 68,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,83; 61,4</t>
+          <t>20,37; 59,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,57; 65,3</t>
+          <t>18,15; 64,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 47,84</t>
+          <t>14,16; 50,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,28; 61,88</t>
+          <t>41,74; 62,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,11; 29,8</t>
+          <t>14,03; 30,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,45; 37,91</t>
+          <t>17,04; 37,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,95; 40,54</t>
+          <t>18,29; 39,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,24; 63,74</t>
+          <t>49,73; 63,71</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,56; 60,63</t>
+          <t>17,29; 64,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,04; 51,44</t>
+          <t>18,45; 49,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,35; 50,89</t>
+          <t>25,08; 50,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,09; 53,39</t>
+          <t>26,75; 53,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 42,29</t>
+          <t>11,78; 40,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,14; 43,75</t>
+          <t>23,39; 44,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,57; 47,28</t>
+          <t>19,53; 48,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,74; 68,64</t>
+          <t>54,69; 67,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,4; 41,34</t>
+          <t>17,13; 40,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,93; 41,5</t>
+          <t>23,92; 41,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25,68; 44,78</t>
+          <t>24,83; 44,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,49; 62,18</t>
+          <t>49,95; 62,19</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>23,49; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,53; 35,64</t>
+          <t>19,85; 35,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,12; 39,28</t>
+          <t>23,4; 39,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,66; 38,41</t>
+          <t>20,98; 37,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54,49; 66,45</t>
+          <t>54,72; 66,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,83; 35,72</t>
+          <t>20,44; 35,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,12; 39,28</t>
+          <t>23,4; 39,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,66; 38,41</t>
+          <t>20,98; 37,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,72; 66,73</t>
+          <t>54,6; 66,85</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,96; 26,41</t>
+          <t>13,87; 28,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,57; 30,96</t>
+          <t>16,53; 31,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,51; 37,22</t>
+          <t>21,89; 36,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45,26; 58,48</t>
+          <t>45,41; 57,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,56; 31,66</t>
+          <t>19,92; 31,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,76; 38,4</t>
+          <t>26,8; 37,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,2; 34,49</t>
+          <t>22,25; 34,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,68; 62,63</t>
+          <t>54,88; 63,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,01; 27,96</t>
+          <t>19,05; 28,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,47; 33,46</t>
+          <t>24,66; 34,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,77; 33,45</t>
+          <t>24,17; 33,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,8; 59,68</t>
+          <t>53,05; 59,72</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda un familiar no conviviente cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6100</t>
+          <t>0; 6319</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3578</t>
+          <t>0; 3580</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 4241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2264; 7736</t>
+          <t>2585; 7896</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1803</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5436</t>
+          <t>0; 5486</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4379; 10076</t>
+          <t>4407; 9975</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7877</t>
+          <t>0; 7551</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5669</t>
+          <t>0; 4537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6802</t>
+          <t>0; 6902</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8108; 15899</t>
+          <t>8317; 16224</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1844</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4615</t>
+          <t>0; 4571</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>816; 6143</t>
+          <t>811; 6287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5371; 11925</t>
+          <t>5110; 11838</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1636</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5296</t>
+          <t>0; 5300</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1773</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3914; 8985</t>
+          <t>3812; 9043</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>864; 7166</t>
+          <t>822; 7133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>803; 6677</t>
+          <t>820; 7516</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10592; 18990</t>
+          <t>10516; 19157</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1836; 9943</t>
+          <t>1854; 9328</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1950; 10641</t>
+          <t>1766; 10456</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>750; 5738</t>
+          <t>724; 5929</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7196; 14120</t>
+          <t>7101; 14305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5382</t>
+          <t>0; 5512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3933; 12398</t>
+          <t>3224; 12526</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1157; 8237</t>
+          <t>1177; 8500</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8608; 15282</t>
+          <t>8240; 15072</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3370; 12809</t>
+          <t>3001; 12184</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7545; 20352</t>
+          <t>7120; 19726</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2789; 12129</t>
+          <t>2539; 11870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18004; 27316</t>
+          <t>17648; 27475</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5908; 16711</t>
+          <t>6352; 17435</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8603; 23695</t>
+          <t>9090; 22696</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6689; 16996</t>
+          <t>7283; 17057</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36046; 49223</t>
+          <t>35754; 49086</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4878; 14380</t>
+          <t>4772; 13934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4078; 13608</t>
+          <t>3782; 13508</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4093; 15703</t>
+          <t>4647; 16543</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16399; 23999</t>
+          <t>16189; 24302</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13273; 28022</t>
+          <t>13196; 28294</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16349; 33597</t>
+          <t>15099; 32861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13775; 29466</t>
+          <t>13297; 28935</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54562; 70632</t>
+          <t>55112; 70601</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2824; 9749</t>
+          <t>2780; 10427</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7220; 18535</t>
+          <t>6648; 17967</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11999; 24087</t>
+          <t>11868; 24132</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7845; 16054</t>
+          <t>8043; 15984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4393; 15398</t>
+          <t>4289; 14925</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19331; 36559</t>
+          <t>19546; 37107</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10378; 25070</t>
+          <t>10354; 25583</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51018; 63975</t>
+          <t>50971; 63265</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8611; 21702</t>
+          <t>8994; 21184</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28613; 49635</t>
+          <t>28609; 49356</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25766; 44931</t>
+          <t>24916; 44625</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61003; 76651</t>
+          <t>61568; 76661</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>209; 914</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2145</t>
+          <t>504; 2145</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29577; 51345</t>
+          <t>28591; 50628</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33090; 56215</t>
+          <t>33485; 55896</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31890; 56565</t>
+          <t>30902; 55294</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>76834; 93691</t>
+          <t>77161; 94295</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30197; 51774</t>
+          <t>29632; 51168</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33090; 56215</t>
+          <t>33485; 55896</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31890; 56565</t>
+          <t>30902; 55294</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>78336; 95517</t>
+          <t>78157; 95686</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16410; 33428</t>
+          <t>17560; 35546</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24227; 45248</t>
+          <t>24159; 46071</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26123; 45209</t>
+          <t>26582; 44854</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70100; 90578</t>
+          <t>70327; 89301</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45180; 73115</t>
+          <t>45999; 73873</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74556; 106973</t>
+          <t>74663; 105428</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58634; 91099</t>
+          <t>58786; 90406</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>175929; 201522</t>
+          <t>176574; 203044</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67956; 99972</t>
+          <t>68120; 100743</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>103940; 142106</t>
+          <t>104741; 144511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91648; 128983</t>
+          <t>93192; 130761</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>251660; 284452</t>
+          <t>252859; 284646</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$familiar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$familiar-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,3</t>
+          <t>0,0; 60,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,62</t>
+          <t>0,0; 42,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,35</t>
+          <t>0,0; 61,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,55; 65,82</t>
+          <t>19,14; 63,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,19</t>
+          <t>0,0; 68,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,8; 71,98</t>
+          <t>30,51; 71,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,12</t>
+          <t>0,0; 28,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,9</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,79</t>
+          <t>0,0; 43,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,17; 62,75</t>
+          <t>31,73; 61,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,07</t>
+          <t>0,0; 54,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 58,46</t>
+          <t>7,46; 59,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,27; 67,81</t>
+          <t>27,72; 66,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,17</t>
+          <t>0,0; 60,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,79; 65,92</t>
+          <t>23,73; 62,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 38,94</t>
+          <t>4,72; 39,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 43,04</t>
+          <t>4,67; 36,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,73; 61,45</t>
+          <t>31,81; 60,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 51,77</t>
+          <t>10,21; 55,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 42,79</t>
+          <t>7,72; 50,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 35,97</t>
+          <t>4,26; 34,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,51; 67,52</t>
+          <t>34,53; 67,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,25</t>
+          <t>0,0; 67,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,97; 65,92</t>
+          <t>17,07; 61,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 52,15</t>
+          <t>7,33; 53,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,91; 71,16</t>
+          <t>38,8; 69,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 46,26</t>
+          <t>12,53; 47,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 45,41</t>
+          <t>15,98; 44,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 36,21</t>
+          <t>7,15; 36,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,66; 64,85</t>
+          <t>41,88; 64,34</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 24,69</t>
+          <t>8,35; 24,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 33,48</t>
+          <t>13,09; 34,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,27; 42,79</t>
+          <t>18,49; 44,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,63; 68,14</t>
+          <t>48,73; 67,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,37; 59,49</t>
+          <t>20,93; 59,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,15; 64,83</t>
+          <t>16,53; 65,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,16; 50,4</t>
+          <t>13,21; 49,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,74; 62,66</t>
+          <t>42,09; 63,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 30,08</t>
+          <t>13,26; 28,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 37,08</t>
+          <t>17,56; 36,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 39,81</t>
+          <t>19,96; 41,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,73; 63,71</t>
+          <t>48,52; 63,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,29; 64,85</t>
+          <t>17,68; 60,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,45; 49,86</t>
+          <t>17,64; 50,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,08; 50,99</t>
+          <t>24,85; 51,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,75; 53,16</t>
+          <t>25,79; 53,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,78; 40,99</t>
+          <t>11,32; 40,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,39; 44,41</t>
+          <t>22,7; 44,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,53; 48,25</t>
+          <t>18,97; 47,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,69; 67,88</t>
+          <t>53,73; 67,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 40,36</t>
+          <t>16,97; 43,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,92; 41,27</t>
+          <t>24,46; 40,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,83; 44,47</t>
+          <t>25,74; 44,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,95; 62,19</t>
+          <t>48,78; 61,41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,12%</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,49; 100,0</t>
+          <t>14,82; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,85; 35,15</t>
+          <t>19,91; 35,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,4; 39,06</t>
+          <t>22,86; 39,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,98; 37,55</t>
+          <t>21,33; 37,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>54,72; 66,88</t>
+          <t>53,97; 66,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20,44; 35,3</t>
+          <t>19,84; 35,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,4; 39,06</t>
+          <t>22,86; 39,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20,98; 37,55</t>
+          <t>21,33; 37,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54,6; 66,85</t>
+          <t>54,21; 65,76</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,87; 28,08</t>
+          <t>13,68; 27,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,53; 31,52</t>
+          <t>16,22; 31,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,89; 36,93</t>
+          <t>21,9; 36,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45,41; 57,66</t>
+          <t>44,32; 57,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,92; 31,99</t>
+          <t>19,9; 31,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,8; 37,85</t>
+          <t>26,72; 38,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,25; 34,22</t>
+          <t>22,37; 35,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54,88; 63,11</t>
+          <t>53,73; 61,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,05; 28,18</t>
+          <t>19,27; 28,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24,66; 34,02</t>
+          <t>24,57; 33,39</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,17; 33,91</t>
+          <t>23,91; 33,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,05; 59,72</t>
+          <t>51,45; 58,59</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>12515</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6319</t>
+          <t>0; 6139</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3580</t>
+          <t>0; 3581</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4241</t>
+          <t>0; 4327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2585; 7896</t>
+          <t>2393; 7918</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1957,32 +1957,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5486</t>
+          <t>0; 5546</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4407; 9975</t>
+          <t>4574; 10772</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 7551</t>
+          <t>0; 6705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4537</t>
+          <t>0; 4501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6902</t>
+          <t>0; 6593</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8317; 16224</t>
+          <t>8723; 17005</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>15323</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4571</t>
+          <t>0; 5162</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>811; 6287</t>
+          <t>802; 6347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5110; 11838</t>
+          <t>5201; 12544</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 5286</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3812; 9043</t>
+          <t>3685; 9662</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>822; 7133</t>
+          <t>864; 7181</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>820; 7516</t>
+          <t>816; 6446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10516; 19157</t>
+          <t>10909; 20755</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22656</t>
+          <t>24723</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1854; 9328</t>
+          <t>1840; 9996</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1766; 10456</t>
+          <t>1886; 12223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>724; 5929</t>
+          <t>702; 5757</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7101; 14305</t>
+          <t>7869; 15450</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5512</t>
+          <t>0; 5588</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3224; 12526</t>
+          <t>3243; 11740</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1177; 8500</t>
+          <t>1195; 8662</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8240; 15072</t>
+          <t>9264; 16594</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3001; 12184</t>
+          <t>3301; 12617</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7120; 19726</t>
+          <t>6943; 19252</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2539; 11870</t>
+          <t>2343; 11868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17648; 27475</t>
+          <t>19544; 30026</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42678</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62903</t>
+          <t>66798</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6352; 17435</t>
+          <t>5899; 17528</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9090; 22696</t>
+          <t>8877; 23323</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7283; 17057</t>
+          <t>7370; 17557</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35754; 49086</t>
+          <t>37592; 51976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4772; 13934</t>
+          <t>4902; 14015</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3782; 13508</t>
+          <t>3445; 13629</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4647; 16543</t>
+          <t>4338; 16371</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16189; 24302</t>
+          <t>17611; 26411</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13196; 28294</t>
+          <t>12468; 27203</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15099; 32861</t>
+          <t>15566; 32476</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13297; 28935</t>
+          <t>14509; 30180</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>55112; 70601</t>
+          <t>57725; 75936</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>57349</t>
+          <t>61096</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69140</t>
+          <t>73705</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2780; 10427</t>
+          <t>2843; 9784</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6648; 17967</t>
+          <t>6356; 18018</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11868; 24132</t>
+          <t>11759; 24293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8043; 15984</t>
+          <t>8481; 17437</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4289; 14925</t>
+          <t>4124; 14713</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19546; 37107</t>
+          <t>18966; 36968</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10354; 25583</t>
+          <t>10058; 25034</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50971; 63265</t>
+          <t>54124; 68209</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8994; 21184</t>
+          <t>8911; 22953</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28609; 49356</t>
+          <t>29252; 48965</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24916; 44625</t>
+          <t>25832; 45146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61568; 76661</t>
+          <t>65173; 82052</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>85739</t>
+          <t>91066</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87352</t>
+          <t>92754</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>504; 2145</t>
+          <t>327; 2204</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28591; 50628</t>
+          <t>28674; 51312</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33485; 55896</t>
+          <t>32718; 56236</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30902; 55294</t>
+          <t>31410; 55633</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>77161; 94295</t>
+          <t>82085; 100593</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29632; 51168</t>
+          <t>28756; 51956</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33485; 55896</t>
+          <t>32718; 56236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30902; 55294</t>
+          <t>31410; 55633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>78157; 95686</t>
+          <t>83637; 101470</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>188743</t>
+          <t>201372</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>268836</t>
+          <t>285819</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17560; 35546</t>
+          <t>17321; 35325</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24159; 46071</t>
+          <t>23707; 45501</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26582; 44854</t>
+          <t>26604; 44783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70327; 89301</t>
+          <t>73692; 95216</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45999; 73873</t>
+          <t>45953; 73648</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74663; 105428</t>
+          <t>74437; 107513</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58786; 90406</t>
+          <t>59092; 92758</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>176574; 203044</t>
+          <t>187554; 214585</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>68120; 100743</t>
+          <t>68901; 101870</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>104741; 144511</t>
+          <t>104347; 141822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93192; 130761</t>
+          <t>92219; 128408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>252859; 284646</t>
+          <t>265153; 301957</t>
         </is>
       </c>
     </row>
